--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49601B65-C3FF-4BFD-A85B-FEBFB918CF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BB8210-F156-4C2C-AD7D-090E281A322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>N° VALE</t>
   </si>
@@ -47,16 +47,25 @@
     <t>ESTADO</t>
   </si>
   <si>
-    <t>PEPITO</t>
-  </si>
-  <si>
-    <t>ATENDIDO</t>
-  </si>
-  <si>
     <t>PROGRAMA</t>
   </si>
   <si>
-    <t>EN CURSO</t>
+    <t>MAR NEGRO</t>
+  </si>
+  <si>
+    <t>NO ATENDIDO</t>
+  </si>
+  <si>
+    <t>MAGALLANES</t>
+  </si>
+  <si>
+    <t>ATLANTICO II</t>
+  </si>
+  <si>
+    <t>ATLANTICO IV</t>
+  </si>
+  <si>
+    <t>ALBATROS</t>
   </si>
 </sst>
 </file>
@@ -444,11 +453,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
-  <dimension ref="B3:E7"/>
+  <dimension ref="B3:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
@@ -459,7 +469,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
@@ -467,42 +477,74 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
-        <v>101</v>
+        <v>1772</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>31231332</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="B5" s="1">
+        <v>1773</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="1">
+        <v>1774</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>101</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>41412321</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
+      <c r="B7" s="1">
+        <v>1775</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1776</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1777</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BB8210-F156-4C2C-AD7D-090E281A322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF68395C-7A39-4BF9-B704-97069866341B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t>N° VALE</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>ALBATROS</t>
+  </si>
+  <si>
+    <t>ATLANTICO I</t>
   </si>
 </sst>
 </file>
@@ -116,9 +119,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
-  <dimension ref="B3:E9"/>
+  <dimension ref="B3:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -547,6 +551,54 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1778</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1779</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1780</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1781</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF68395C-7A39-4BF9-B704-97069866341B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16B62AA-578B-4CBA-8E6B-A1DC0BD5049B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
   <si>
     <t>N° VALE</t>
   </si>
@@ -69,6 +69,33 @@
   </si>
   <si>
     <t>ATLANTICO I</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ILEÑA I</t>
+  </si>
+  <si>
+    <t>ATLANTICO III</t>
+  </si>
+  <si>
+    <t>CH00028287</t>
+  </si>
+  <si>
+    <t>EN CURSO</t>
+  </si>
+  <si>
+    <t>CH00028272</t>
+  </si>
+  <si>
+    <t>CH00028292</t>
+  </si>
+  <si>
+    <t>CH00028289</t>
+  </si>
+  <si>
+    <t>CH00028288</t>
   </si>
 </sst>
 </file>
@@ -457,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
-  <dimension ref="B3:E13"/>
+  <dimension ref="B3:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -522,7 +549,9 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>5</v>
       </c>
@@ -558,7 +587,9 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
@@ -591,13 +622,327 @@
       <c r="B13" s="1">
         <v>1781</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>1782</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1783</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>1784</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>1785</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>1786</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>1787</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>1788</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>2801</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>2802</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
+        <v>2803</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>2804</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
+        <v>2805</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>2806</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <v>2807</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>2808</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="1">
+        <v>2809</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>2810</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="1">
+        <v>2811</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>2812</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="1">
+        <v>2813</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>2814</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="1">
+        <v>2815</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>2816</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="1">
+        <v>2817</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <v>2818</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="1">
+        <v>2819</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="2">
+        <v>2820</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="1">
+        <v>2821</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="2">
+        <v>2822</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="1">
+        <v>2823</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <v>2824</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="1">
+        <v>2825</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>2826</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16B62AA-578B-4CBA-8E6B-A1DC0BD5049B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C02BACB-55A3-43DD-9015-AEF994101CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
@@ -553,7 +553,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -591,7 +591,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -641,7 +641,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -741,7 +741,7 @@
         <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">

--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C02BACB-55A3-43DD-9015-AEF994101CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D21B6B-2BB2-4B94-A4FD-21696E0BB83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
   <si>
     <t>N° VALE</t>
   </si>
@@ -96,6 +96,21 @@
   </si>
   <si>
     <t>CH00028288</t>
+  </si>
+  <si>
+    <t>CH00028299</t>
+  </si>
+  <si>
+    <t>CH00002898</t>
+  </si>
+  <si>
+    <t>CH00028304</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>SEDE</t>
   </si>
 </sst>
 </file>
@@ -484,15 +499,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
-  <dimension ref="B3:E46"/>
+  <dimension ref="B3:F49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,10 +518,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>1772</v>
       </c>
@@ -514,23 +532,29 @@
         <v>4</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>1773</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>1774</v>
       </c>
@@ -538,11 +562,12 @@
         <v>7</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>1775</v>
       </c>
@@ -553,10 +578,13 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>1776</v>
       </c>
@@ -564,11 +592,12 @@
         <v>8</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>1777</v>
       </c>
@@ -576,11 +605,12 @@
         <v>9</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>1778</v>
       </c>
@@ -591,10 +621,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>1779</v>
       </c>
@@ -602,11 +635,12 @@
         <v>7</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>1780</v>
       </c>
@@ -614,11 +648,12 @@
         <v>7</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>1781</v>
       </c>
@@ -626,11 +661,12 @@
         <v>8</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>1782</v>
       </c>
@@ -641,10 +677,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>1783</v>
       </c>
@@ -652,11 +691,12 @@
         <v>4</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>1784</v>
       </c>
@@ -664,11 +704,12 @@
         <v>8</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>1785</v>
       </c>
@@ -676,23 +717,29 @@
         <v>11</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>1786</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>1787</v>
       </c>
@@ -700,11 +747,12 @@
         <v>12</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>1788</v>
       </c>
@@ -712,237 +760,323 @@
         <v>13</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="1">
-        <v>2801</v>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>913</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>916</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>918</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="1">
+        <v>2801</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
         <v>2802</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="1">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="1">
         <v>2803</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="2">
-        <v>2804</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="1">
-        <v>2805</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="2">
-        <v>2806</v>
-      </c>
-      <c r="C26" s="2"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="1">
-        <v>2807</v>
-      </c>
-      <c r="C27" s="2"/>
+      <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>2804</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="2">
-        <v>2808</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="1">
-        <v>2809</v>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="1">
+        <v>2805</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>2806</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="2">
-        <v>2810</v>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="1">
+        <v>2807</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="1">
-        <v>2811</v>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>2808</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="2">
-        <v>2812</v>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="1">
+        <v>2809</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="1">
-        <v>2813</v>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="2">
+        <v>2810</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="2">
-        <v>2814</v>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="1">
+        <v>2811</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="1">
-        <v>2815</v>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="2">
+        <v>2812</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="2">
-        <v>2816</v>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="1">
+        <v>2813</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="1">
-        <v>2817</v>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="2">
+        <v>2814</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="2">
-        <v>2818</v>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="1">
+        <v>2815</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="1">
-        <v>2819</v>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="2">
+        <v>2816</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="2">
-        <v>2820</v>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="1">
+        <v>2817</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="1">
-        <v>2821</v>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <v>2818</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="2">
-        <v>2822</v>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="1">
+        <v>2819</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="1">
-        <v>2823</v>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="2">
+        <v>2820</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B44" s="2">
-        <v>2824</v>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="1">
+        <v>2821</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="1">
-        <v>2825</v>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="2">
+        <v>2822</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="2">
-        <v>2826</v>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46" s="1">
+        <v>2823</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="2">
+        <v>2824</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="1">
+        <v>2825</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="2">
+        <v>2826</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D21B6B-2BB2-4B94-A4FD-21696E0BB83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B97A8A-D1E3-4151-94E4-FB14B09EB0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$F$49</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="27">
   <si>
     <t>N° VALE</t>
   </si>
@@ -111,6 +114,12 @@
   </si>
   <si>
     <t>SEDE</t>
+  </si>
+  <si>
+    <t>ATENDIDO</t>
+  </si>
+  <si>
+    <t>PARCIAL</t>
   </si>
 </sst>
 </file>
@@ -499,6 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B3:F49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -534,10 +544,10 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>1773</v>
       </c>
@@ -554,7 +564,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>1774</v>
       </c>
@@ -567,7 +577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>1775</v>
       </c>
@@ -584,7 +594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>1776</v>
       </c>
@@ -597,7 +607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>1777</v>
       </c>
@@ -610,7 +620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>1778</v>
       </c>
@@ -627,7 +637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>1779</v>
       </c>
@@ -637,10 +647,10 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>1780</v>
       </c>
@@ -653,7 +663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>1781</v>
       </c>
@@ -696,7 +706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>1784</v>
       </c>
@@ -709,7 +719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>1785</v>
       </c>
@@ -722,7 +732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>1786</v>
       </c>
@@ -739,7 +749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>1787</v>
       </c>
@@ -752,7 +762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>1788</v>
       </c>
@@ -765,7 +775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>913</v>
       </c>
@@ -778,7 +788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>916</v>
       </c>
@@ -795,7 +805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>918</v>
       </c>
@@ -812,7 +822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>2801</v>
       </c>
@@ -829,7 +839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>2802</v>
       </c>
@@ -846,7 +856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>2803</v>
       </c>
@@ -859,7 +869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>2804</v>
       </c>
@@ -869,10 +879,10 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>2805</v>
       </c>
@@ -886,10 +896,10 @@
         <v>23</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>2806</v>
       </c>
@@ -898,7 +908,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>2807</v>
       </c>
@@ -907,7 +917,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>2808</v>
       </c>
@@ -916,7 +926,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>2809</v>
       </c>
@@ -925,7 +935,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>2810</v>
       </c>
@@ -934,7 +944,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <v>2811</v>
       </c>
@@ -943,7 +953,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>2812</v>
       </c>
@@ -952,7 +962,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>2813</v>
       </c>
@@ -961,7 +971,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>2814</v>
       </c>
@@ -970,7 +980,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1">
         <v>2815</v>
       </c>
@@ -979,7 +989,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <v>2816</v>
       </c>
@@ -988,7 +998,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <v>2817</v>
       </c>
@@ -997,7 +1007,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <v>2818</v>
       </c>
@@ -1006,7 +1016,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <v>2819</v>
       </c>
@@ -1015,7 +1025,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>2820</v>
       </c>
@@ -1024,7 +1034,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
         <v>2821</v>
       </c>
@@ -1033,7 +1043,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>2822</v>
       </c>
@@ -1042,7 +1052,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
         <v>2823</v>
       </c>
@@ -1051,7 +1061,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>2824</v>
       </c>
@@ -1060,7 +1070,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
         <v>2825</v>
       </c>
@@ -1069,7 +1079,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>2826</v>
       </c>
@@ -1079,6 +1089,13 @@
       <c r="F49" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="B3:F49" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="MAR NEGRO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PEDIDOS.xlsx
+++ b/PEDIDOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LP-KEVIN-PALOMINO\OneDrive\Documents\2026\KEVIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B97A8A-D1E3-4151-94E4-FB14B09EB0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B4CBD3-63CA-43B3-A32A-B7F52B1A43E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB08F6C-ADA4-4925-AC2B-60267B377846}"/>
   </bookViews>
@@ -508,7 +508,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
-  <sheetPr filterMode="1"/>
   <dimension ref="B3:F49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -547,7 +546,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>1773</v>
       </c>
@@ -564,7 +563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>1774</v>
       </c>
@@ -577,7 +576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>1775</v>
       </c>
@@ -594,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>1776</v>
       </c>
@@ -607,7 +606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>1777</v>
       </c>
@@ -620,7 +619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>1778</v>
       </c>
@@ -637,7 +636,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>1779</v>
       </c>
@@ -650,7 +649,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>1780</v>
       </c>
@@ -663,7 +662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>1781</v>
       </c>
@@ -706,7 +705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>1784</v>
       </c>
@@ -719,7 +718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>1785</v>
       </c>
@@ -732,7 +731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>1786</v>
       </c>
@@ -749,7 +748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>1787</v>
       </c>
@@ -762,7 +761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>1788</v>
       </c>
@@ -775,7 +774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>913</v>
       </c>
@@ -788,7 +787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>916</v>
       </c>
@@ -805,7 +804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>918</v>
       </c>
@@ -822,7 +821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>2801</v>
       </c>
@@ -839,7 +838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>2802</v>
       </c>
@@ -856,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>2803</v>
       </c>
@@ -869,7 +868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>2804</v>
       </c>
@@ -882,7 +881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>2805</v>
       </c>
@@ -899,7 +898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>2806</v>
       </c>
@@ -908,7 +907,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>2807</v>
       </c>
@@ -917,7 +916,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>2808</v>
       </c>
@@ -926,7 +925,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>2809</v>
       </c>
@@ -935,7 +934,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>2810</v>
       </c>
@@ -944,7 +943,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <v>2811</v>
       </c>
@@ -953,7 +952,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>2812</v>
       </c>
@@ -962,7 +961,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>2813</v>
       </c>
@@ -971,7 +970,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>2814</v>
       </c>
@@ -980,7 +979,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="1">
         <v>2815</v>
       </c>
@@ -989,7 +988,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <v>2816</v>
       </c>
@@ -998,7 +997,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <v>2817</v>
       </c>
@@ -1007,7 +1006,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <v>2818</v>
       </c>
@@ -1016,7 +1015,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <v>2819</v>
       </c>
@@ -1025,7 +1024,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>2820</v>
       </c>
@@ -1034,7 +1033,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
         <v>2821</v>
       </c>
@@ -1043,7 +1042,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>2822</v>
       </c>
@@ -1052,7 +1051,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
         <v>2823</v>
       </c>
@@ -1061,7 +1060,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>2824</v>
       </c>
@@ -1070,7 +1069,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
         <v>2825</v>
       </c>
@@ -1079,7 +1078,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>2826</v>
       </c>
@@ -1089,13 +1088,7 @@
       <c r="F49" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:F49" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="MAR NEGRO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B3:F49" xr:uid="{50DA50AB-B257-4AA5-BA23-3AFB1331FB77}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>